--- a/products-storage/00-free-ks-podpisany-deneg-net/02-kalkulyator-sroka-oplaty.xlsx
+++ b/products-storage/00-free-ks-podpisany-deneg-net/02-kalkulyator-sroka-oplaty.xlsx
@@ -2,10 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Калькулятор срока оплаты" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -15,12 +20,14 @@
   <fonts count="2">
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -33,12 +40,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF366092"/>
+        <fgColor rgb="00366092"/>
+        <bgColor rgb="00366092"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
@@ -59,8 +73,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -175,14 +190,72 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Calibri Light"/>
-        <a:cs typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -238,7 +311,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -247,13 +320,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -287,6 +360,17 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -341,6 +425,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -512,6 +598,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>